--- a/Docs/Ordinals_OULAD.xlsx
+++ b/Docs/Ordinals_OULAD.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jcabral\Downloads\OULAD\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A97BADC4-E043-41B8-8703-1A94E94A8D75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13EDA9BB-0CAB-4EB8-A785-E8BA754D9816}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -112,19 +112,17 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+      <b/>
+      <sz val="12"/>
+      <color theme="0"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
     <font>
-      <b/>
-      <sz val="10"/>
-      <color theme="0"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -260,20 +258,57 @@
   </cellStyleXfs>
   <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="10">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <font>
         <b/>
@@ -285,13 +320,14 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="10"/>
+        <sz val="12"/>
         <color theme="0"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
       </font>
-      <border diagonalUp="0" diagonalDown="0">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
@@ -300,12 +336,6 @@
         </right>
         <top/>
         <bottom/>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
       </border>
     </dxf>
     <dxf>
@@ -319,13 +349,14 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="10"/>
+        <sz val="12"/>
         <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
       </font>
-      <border diagonalUp="0" diagonalDown="0">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
@@ -336,12 +367,6 @@
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
       </border>
     </dxf>
     <dxf>
@@ -355,13 +380,14 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="10"/>
+        <sz val="12"/>
         <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
       </font>
-      <border diagonalUp="0" diagonalDown="0">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
@@ -374,12 +400,6 @@
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
       </border>
     </dxf>
     <dxf>
@@ -393,13 +413,14 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="10"/>
+        <sz val="12"/>
         <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
       </font>
-      <border diagonalUp="0" diagonalDown="0">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
@@ -412,12 +433,6 @@
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
       </border>
     </dxf>
     <dxf>
@@ -431,13 +446,14 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="10"/>
+        <sz val="12"/>
         <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
       </font>
-      <border diagonalUp="0" diagonalDown="0">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
@@ -450,12 +466,6 @@
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
       </border>
     </dxf>
     <dxf>
@@ -469,13 +479,14 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="10"/>
+        <sz val="12"/>
         <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
       </font>
-      <border diagonalUp="0" diagonalDown="0">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
         <left/>
         <right style="thin">
           <color indexed="64"/>
@@ -486,12 +497,6 @@
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
       </border>
     </dxf>
     <dxf>
@@ -502,45 +507,27 @@
       </border>
     </dxf>
     <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
       <border>
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
       </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -556,14 +543,14 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{AA942C03-2358-410C-B62B-ED02B9C1F467}" name="Table1" displayName="Table1" ref="A1:E7" totalsRowShown="0" headerRowDxfId="0" dataDxfId="9" headerRowBorderDxfId="7" tableBorderDxfId="8" totalsRowBorderDxfId="6">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{AA942C03-2358-410C-B62B-ED02B9C1F467}" name="Table1" displayName="Table1" ref="A1:E7" totalsRowShown="0" headerRowDxfId="1" dataDxfId="0" headerRowBorderDxfId="9" tableBorderDxfId="8" totalsRowBorderDxfId="7">
   <autoFilter ref="A1:E7" xr:uid="{AA942C03-2358-410C-B62B-ED02B9C1F467}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{110C57CB-305E-4226-825B-6D9A2E5BE25C}" name="Tabla" dataDxfId="5"/>
-    <tableColumn id="2" xr3:uid="{28F52B37-1EE5-4A05-92A1-C0FA71CC0DBB}" name="Columna Actual" dataDxfId="4"/>
-    <tableColumn id="3" xr3:uid="{F5C26D78-5409-4DC6-8FF5-1BB6E133E36B}" name="Tipo de Variable" dataDxfId="3"/>
-    <tableColumn id="4" xr3:uid="{0D18914C-1A10-4099-ABFB-8940107F8064}" name="Nueva Clasificación (Mapeo Numérico)" dataDxfId="2"/>
-    <tableColumn id="5" xr3:uid="{D7CB8A74-B7D9-41AC-AA1F-EF0D37E4D0CB}" name="Nuevo Nombre Columna" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{110C57CB-305E-4226-825B-6D9A2E5BE25C}" name="Tabla" dataDxfId="6"/>
+    <tableColumn id="2" xr3:uid="{28F52B37-1EE5-4A05-92A1-C0FA71CC0DBB}" name="Columna Actual" dataDxfId="5"/>
+    <tableColumn id="3" xr3:uid="{F5C26D78-5409-4DC6-8FF5-1BB6E133E36B}" name="Tipo de Variable" dataDxfId="4"/>
+    <tableColumn id="4" xr3:uid="{0D18914C-1A10-4099-ABFB-8940107F8064}" name="Nueva Clasificación (Mapeo Numérico)" dataDxfId="3"/>
+    <tableColumn id="5" xr3:uid="{D7CB8A74-B7D9-41AC-AA1F-EF0D37E4D0CB}" name="Nuevo Nombre Columna" dataDxfId="2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -773,14 +760,14 @@
   <dimension ref="A1:E7"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.5703125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="18.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="112" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="25.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="138.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="27.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -797,7 +784,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>5</v>
       </c>
@@ -814,7 +801,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>5</v>
       </c>
@@ -831,7 +818,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>5</v>
       </c>
@@ -848,7 +835,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>5</v>
       </c>
@@ -865,7 +852,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>5</v>
       </c>
@@ -882,7 +869,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
         <v>5</v>
       </c>
